--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H273"/>
+  <dimension ref="A1:H274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7522,6 +7522,32 @@
         <v>2.054634889032031</v>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B274" t="n">
+        <v>248500</v>
+      </c>
+      <c r="C274" t="n">
+        <v>17757600</v>
+      </c>
+      <c r="D274" t="n">
+        <v>250330</v>
+      </c>
+      <c r="E274" t="n">
+        <v>262396</v>
+      </c>
+      <c r="F274" t="n">
+        <v>263889</v>
+      </c>
+      <c r="G274" t="n">
+        <v>258872</v>
+      </c>
+      <c r="H274" t="n">
+        <v>2.031820577384786</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H274"/>
+  <dimension ref="A1:H275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7548,6 +7548,32 @@
         <v>2.031820577384786</v>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B275" t="n">
+        <v>249000</v>
+      </c>
+      <c r="C275" t="n">
+        <v>9357017</v>
+      </c>
+      <c r="D275" t="n">
+        <v>249613</v>
+      </c>
+      <c r="E275" t="n">
+        <v>262086</v>
+      </c>
+      <c r="F275" t="n">
+        <v>260551</v>
+      </c>
+      <c r="G275" t="n">
+        <v>257417</v>
+      </c>
+      <c r="H275" t="n">
+        <v>2.014780113603092</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>260500</v>
+        <v>261000</v>
       </c>
       <c r="C419" t="n">
-        <v>8851329</v>
+        <v>17104876</v>
       </c>
       <c r="D419" t="n">
-        <v>249644</v>
+        <v>249738</v>
       </c>
       <c r="E419" t="n">
-        <v>261155</v>
+        <v>261163</v>
       </c>
       <c r="F419" t="n">
-        <v>252163</v>
+        <v>253306</v>
       </c>
       <c r="G419" t="n">
-        <v>254321</v>
+        <v>254735</v>
       </c>
       <c r="H419" t="n">
-        <v>1.978520817473795</v>
+        <v>1.983369444281783</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>1.983369444281783</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>274000</v>
+      </c>
+      <c r="C420" t="n">
+        <v>21569691</v>
+      </c>
+      <c r="D420" t="n">
+        <v>250218</v>
+      </c>
+      <c r="E420" t="n">
+        <v>260526</v>
+      </c>
+      <c r="F420" t="n">
+        <v>260427</v>
+      </c>
+      <c r="G420" t="n">
+        <v>257057</v>
+      </c>
+      <c r="H420" t="n">
+        <v>2.010563916378755</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>280750</v>
+        <v>276500</v>
       </c>
       <c r="C421" t="n">
-        <v>2020948</v>
+        <v>17082237</v>
       </c>
       <c r="D421" t="n">
-        <v>250050</v>
+        <v>250435</v>
       </c>
       <c r="E421" t="n">
-        <v>260637</v>
+        <v>261239</v>
       </c>
       <c r="F421" t="n">
-        <v>263150</v>
+        <v>265596</v>
       </c>
       <c r="G421" t="n">
-        <v>257946</v>
+        <v>259090</v>
       </c>
       <c r="H421" t="n">
-        <v>2.020975581191076</v>
+        <v>2.034373719037302</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>2.034373719037302</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>285500</v>
+      </c>
+      <c r="C422" t="n">
+        <v>20085417</v>
+      </c>
+      <c r="D422" t="n">
+        <v>250820</v>
+      </c>
+      <c r="E422" t="n">
+        <v>262450</v>
+      </c>
+      <c r="F422" t="n">
+        <v>271776</v>
+      </c>
+      <c r="G422" t="n">
+        <v>261682</v>
+      </c>
+      <c r="H422" t="n">
+        <v>2.064730339052527</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>2.064730339052527</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>270000</v>
+      </c>
+      <c r="C423" t="n">
+        <v>20513212</v>
+      </c>
+      <c r="D423" t="n">
+        <v>252553</v>
+      </c>
+      <c r="E423" t="n">
+        <v>263997</v>
+      </c>
+      <c r="F423" t="n">
+        <v>273681</v>
+      </c>
+      <c r="G423" t="n">
+        <v>263410</v>
+      </c>
+      <c r="H423" t="n">
+        <v>2.084968085729344</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>2.084968085729344</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>272500</v>
+      </c>
+      <c r="C424" t="n">
+        <v>15258124</v>
+      </c>
+      <c r="D424" t="n">
+        <v>256120</v>
+      </c>
+      <c r="E424" t="n">
+        <v>264387</v>
+      </c>
+      <c r="F424" t="n">
+        <v>275786</v>
+      </c>
+      <c r="G424" t="n">
+        <v>265431</v>
+      </c>
+      <c r="H424" t="n">
+        <v>2.108637348480412</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>2.108637348480412</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>268500</v>
+      </c>
+      <c r="C425" t="n">
+        <v>15961193</v>
+      </c>
+      <c r="D425" t="n">
+        <v>258749</v>
+      </c>
+      <c r="E425" t="n">
+        <v>264828</v>
+      </c>
+      <c r="F425" t="n">
+        <v>274911</v>
+      </c>
+      <c r="G425" t="n">
+        <v>266163</v>
+      </c>
+      <c r="H425" t="n">
+        <v>2.117210282836564</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -11444,22 +11444,22 @@
         <v>268500</v>
       </c>
       <c r="C425" t="n">
-        <v>15961193</v>
+        <v>16022228</v>
       </c>
       <c r="D425" t="n">
-        <v>258749</v>
+        <v>258750</v>
       </c>
       <c r="E425" t="n">
-        <v>264828</v>
+        <v>264829</v>
       </c>
       <c r="F425" t="n">
-        <v>274911</v>
+        <v>274906</v>
       </c>
       <c r="G425" t="n">
-        <v>266163</v>
+        <v>266162</v>
       </c>
       <c r="H425" t="n">
-        <v>2.117210282836564</v>
+        <v>2.117198571177607</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>2.117198571177607</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>276000</v>
+      </c>
+      <c r="C426" t="n">
+        <v>13164410</v>
+      </c>
+      <c r="D426" t="n">
+        <v>259027</v>
+      </c>
+      <c r="E426" t="n">
+        <v>265455</v>
+      </c>
+      <c r="F426" t="n">
+        <v>274755</v>
+      </c>
+      <c r="G426" t="n">
+        <v>266413</v>
+      </c>
+      <c r="H426" t="n">
+        <v>2.120138197575687</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>276000</v>
+      </c>
+      <c r="C427" t="n">
+        <v>11236638</v>
+      </c>
+      <c r="D427" t="n">
+        <v>259257</v>
+      </c>
+      <c r="E427" t="n">
+        <v>266521</v>
+      </c>
+      <c r="F427" t="n">
+        <v>272107</v>
+      </c>
+      <c r="G427" t="n">
+        <v>265961</v>
+      </c>
+      <c r="H427" t="n">
+        <v>2.114844527727353</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>2.114844527727353</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>272000</v>
+      </c>
+      <c r="C428" t="n">
+        <v>12691976</v>
+      </c>
+      <c r="D428" t="n">
+        <v>262416</v>
+      </c>
+      <c r="E428" t="n">
+        <v>267981</v>
+      </c>
+      <c r="F428" t="n">
+        <v>272719</v>
+      </c>
+      <c r="G428" t="n">
+        <v>267705</v>
+      </c>
+      <c r="H428" t="n">
+        <v>2.135269660947473</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>2.135269660947473</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>268500</v>
+      </c>
+      <c r="C429" t="n">
+        <v>15953736</v>
+      </c>
+      <c r="D429" t="n">
+        <v>263430</v>
+      </c>
+      <c r="E429" t="n">
+        <v>267887</v>
+      </c>
+      <c r="F429" t="n">
+        <v>271793</v>
+      </c>
+      <c r="G429" t="n">
+        <v>267703</v>
+      </c>
+      <c r="H429" t="n">
+        <v>2.13524623762956</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>2.13524623762956</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>262000</v>
+      </c>
+      <c r="C430" t="n">
+        <v>20664822</v>
+      </c>
+      <c r="D430" t="n">
+        <v>263391</v>
+      </c>
+      <c r="E430" t="n">
+        <v>267368</v>
+      </c>
+      <c r="F430" t="n">
+        <v>269763</v>
+      </c>
+      <c r="G430" t="n">
+        <v>266841</v>
+      </c>
+      <c r="H430" t="n">
+        <v>2.125150787609065</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>2.125150787609065</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>250500</v>
+      </c>
+      <c r="C431" t="n">
+        <v>19085236</v>
+      </c>
+      <c r="D431" t="n">
+        <v>264908</v>
+      </c>
+      <c r="E431" t="n">
+        <v>266320</v>
+      </c>
+      <c r="F431" t="n">
+        <v>264115</v>
+      </c>
+      <c r="G431" t="n">
+        <v>265115</v>
+      </c>
+      <c r="H431" t="n">
+        <v>2.104936464250161</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>2.104936464250161</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>232000</v>
+      </c>
+      <c r="C432" t="n">
+        <v>25547387</v>
+      </c>
+      <c r="D432" t="n">
+        <v>263541</v>
+      </c>
+      <c r="E432" t="n">
+        <v>263364</v>
+      </c>
+      <c r="F432" t="n">
+        <v>253960</v>
+      </c>
+      <c r="G432" t="n">
+        <v>260288</v>
+      </c>
+      <c r="H432" t="n">
+        <v>2.048404286467178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>2.048404286467178</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>232000</v>
+      </c>
+      <c r="C433" t="n">
+        <v>18488809</v>
+      </c>
+      <c r="D433" t="n">
+        <v>262355</v>
+      </c>
+      <c r="E433" t="n">
+        <v>262219</v>
+      </c>
+      <c r="F433" t="n">
+        <v>247594</v>
+      </c>
+      <c r="G433" t="n">
+        <v>257390</v>
+      </c>
+      <c r="H433" t="n">
+        <v>2.014463898811266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>2.014463898811266</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>210000</v>
+      </c>
+      <c r="C434" t="n">
+        <v>32372165</v>
+      </c>
+      <c r="D434" t="n">
+        <v>260016</v>
+      </c>
+      <c r="E434" t="n">
+        <v>257409</v>
+      </c>
+      <c r="F434" t="n">
+        <v>234246</v>
+      </c>
+      <c r="G434" t="n">
+        <v>250557</v>
+      </c>
+      <c r="H434" t="n">
+        <v>1.934438133161562</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>1.934438133161562</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>215500</v>
+      </c>
+      <c r="C435" t="n">
+        <v>18330009</v>
+      </c>
+      <c r="D435" t="n">
+        <v>258917</v>
+      </c>
+      <c r="E435" t="n">
+        <v>255195</v>
+      </c>
+      <c r="F435" t="n">
+        <v>226188</v>
+      </c>
+      <c r="G435" t="n">
+        <v>246767</v>
+      </c>
+      <c r="H435" t="n">
+        <v>1.890050945716461</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>1.890050945716461</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>218000</v>
+      </c>
+      <c r="C436" t="n">
+        <v>16241690</v>
+      </c>
+      <c r="D436" t="n">
+        <v>258020</v>
+      </c>
+      <c r="E436" t="n">
+        <v>253054</v>
+      </c>
+      <c r="F436" t="n">
+        <v>220809</v>
+      </c>
+      <c r="G436" t="n">
+        <v>243961</v>
+      </c>
+      <c r="H436" t="n">
+        <v>1.857188030684546</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>1.857188030684546</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>211500</v>
+      </c>
+      <c r="C437" t="n">
+        <v>15701751</v>
+      </c>
+      <c r="D437" t="n">
+        <v>256496</v>
+      </c>
+      <c r="E437" t="n">
+        <v>251077</v>
+      </c>
+      <c r="F437" t="n">
+        <v>216536</v>
+      </c>
+      <c r="G437" t="n">
+        <v>241370</v>
+      </c>
+      <c r="H437" t="n">
+        <v>1.826843122328278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>1.826843122328278</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>223500</v>
+      </c>
+      <c r="C438" t="n">
+        <v>16718500</v>
+      </c>
+      <c r="D438" t="n">
+        <v>254692</v>
+      </c>
+      <c r="E438" t="n">
+        <v>248139</v>
+      </c>
+      <c r="F438" t="n">
+        <v>214831</v>
+      </c>
+      <c r="G438" t="n">
+        <v>239220</v>
+      </c>
+      <c r="H438" t="n">
+        <v>1.801663055571822</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>1.801663055571822</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>214500</v>
+      </c>
+      <c r="C439" t="n">
+        <v>11032576</v>
+      </c>
+      <c r="D439" t="n">
+        <v>254060</v>
+      </c>
+      <c r="E439" t="n">
+        <v>245458</v>
+      </c>
+      <c r="F439" t="n">
+        <v>216788</v>
+      </c>
+      <c r="G439" t="n">
+        <v>238768</v>
+      </c>
+      <c r="H439" t="n">
+        <v>1.796369385723488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>1.796369385723488</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>215500</v>
+      </c>
+      <c r="C440" t="n">
+        <v>15684207</v>
+      </c>
+      <c r="D440" t="n">
+        <v>253216</v>
+      </c>
+      <c r="E440" t="n">
+        <v>241409</v>
+      </c>
+      <c r="F440" t="n">
+        <v>216833</v>
+      </c>
+      <c r="G440" t="n">
+        <v>237153</v>
+      </c>
+      <c r="H440" t="n">
+        <v>1.777455056508754</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>1.777455056508754</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>213000</v>
+      </c>
+      <c r="C441" t="n">
+        <v>10938906</v>
+      </c>
+      <c r="D441" t="n">
+        <v>251984</v>
+      </c>
+      <c r="E441" t="n">
+        <v>240455</v>
+      </c>
+      <c r="F441" t="n">
+        <v>215965</v>
+      </c>
+      <c r="G441" t="n">
+        <v>236134</v>
+      </c>
+      <c r="H441" t="n">
+        <v>1.76552087603209</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>1.76552087603209</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>222000</v>
+      </c>
+      <c r="C442" t="n">
+        <v>13550202</v>
+      </c>
+      <c r="D442" t="n">
+        <v>250998</v>
+      </c>
+      <c r="E442" t="n">
+        <v>239717</v>
+      </c>
+      <c r="F442" t="n">
+        <v>218201</v>
+      </c>
+      <c r="G442" t="n">
+        <v>236305</v>
+      </c>
+      <c r="H442" t="n">
+        <v>1.76752356971365</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>1.76752356971365</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>242000</v>
+      </c>
+      <c r="C443" t="n">
+        <v>16880450</v>
+      </c>
+      <c r="D443" t="n">
+        <v>250627</v>
+      </c>
+      <c r="E443" t="n">
+        <v>237981</v>
+      </c>
+      <c r="F443" t="n">
+        <v>222800</v>
+      </c>
+      <c r="G443" t="n">
+        <v>237136</v>
+      </c>
+      <c r="H443" t="n">
+        <v>1.777255958306494</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>1.777255958306494</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>232000</v>
+      </c>
+      <c r="C444" t="n">
+        <v>24295001</v>
+      </c>
+      <c r="D444" t="n">
+        <v>249958</v>
+      </c>
+      <c r="E444" t="n">
+        <v>236031</v>
+      </c>
+      <c r="F444" t="n">
+        <v>226673</v>
+      </c>
+      <c r="G444" t="n">
+        <v>237554</v>
+      </c>
+      <c r="H444" t="n">
+        <v>1.782151431750307</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성전자_일별_기준주가.xlsx
+++ b/data/삼성전자_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>1.782151431750307</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>225000</v>
+      </c>
+      <c r="C445" t="n">
+        <v>19186681</v>
+      </c>
+      <c r="D445" t="n">
+        <v>249271</v>
+      </c>
+      <c r="E445" t="n">
+        <v>233926</v>
+      </c>
+      <c r="F445" t="n">
+        <v>228360</v>
+      </c>
+      <c r="G445" t="n">
+        <v>237186</v>
+      </c>
+      <c r="H445" t="n">
+        <v>1.777841541254319</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
